--- a/Ticket Image/超市小票识别_2026-03-23.xlsx
+++ b/Ticket Image/超市小票识别_2026-03-23.xlsx
@@ -397,107 +397,94 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:F11"/>
   <cols>
-    <col min="1" max="1" width="16.83203125" customWidth="1"/>
-    <col min="2" max="2" width="18.83203125" customWidth="1"/>
+    <col min="1" max="1" width="18.83203125" customWidth="1"/>
+    <col min="2" max="2" width="20.83203125" customWidth="1"/>
     <col min="3" max="3" width="24.83203125" customWidth="1"/>
-    <col min="4" max="4" width="10.83203125" customWidth="1"/>
+    <col min="4" max="4" width="8.83203125" customWidth="1"/>
     <col min="5" max="5" width="10.83203125" customWidth="1"/>
     <col min="6" max="6" width="10.83203125" customWidth="1"/>
-    <col min="7" max="7" width="12.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>大利家精品超市谢村店</v>
+        <v>购物时间</v>
       </c>
       <c r="B1" t="str">
-        <v>2026-03-19 10:43:57</v>
+        <v>超市名称</v>
       </c>
       <c r="C1" t="str">
-        <v/>
+        <v>商品名称</v>
       </c>
       <c r="D1" t="str">
-        <v/>
+        <v>数量</v>
       </c>
       <c r="E1" t="str">
-        <v/>
+        <v>单价</v>
       </c>
       <c r="F1" t="str">
-        <v/>
-      </c>
-      <c r="G1" t="str">
-        <v/>
+        <v>小计</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v/>
+        <v>2026-03-19 10:43:57</v>
       </c>
       <c r="B2" t="str">
-        <v/>
+        <v>大利家精品超市谢村店</v>
       </c>
       <c r="C2" t="str">
-        <v>商品名称</v>
-      </c>
-      <c r="D2" t="str">
-        <v>单价</v>
-      </c>
-      <c r="E2" t="str">
-        <v>数量</v>
-      </c>
-      <c r="F2" t="str">
-        <v>小计</v>
-      </c>
-      <c r="G2" t="str">
-        <v/>
+        <v>鸡腿</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2">
+        <v>7.8</v>
+      </c>
+      <c r="F2">
+        <v>7.8</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v/>
+        <v>2026-03-19 10:43:57</v>
       </c>
       <c r="B3" t="str">
-        <v/>
+        <v>大利家精品超市谢村店</v>
       </c>
       <c r="C3" t="str">
-        <v>鸡腿</v>
+        <v>西兰花</v>
       </c>
       <c r="D3">
-        <v>7.8</v>
+        <v>1</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>3.4</v>
       </c>
       <c r="F3">
-        <v>7.8</v>
-      </c>
-      <c r="G3" t="str">
-        <v/>
+        <v>3.4</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v/>
+        <v>2026-03-19 10:43:57</v>
       </c>
       <c r="B4" t="str">
-        <v/>
+        <v>大利家精品超市谢村店</v>
       </c>
       <c r="C4" t="str">
-        <v>西兰花</v>
-      </c>
-      <c r="D4">
-        <v>3.4</v>
-      </c>
-      <c r="E4">
-        <v>1</v>
+        <v>合计</v>
+      </c>
+      <c r="D4" t="str">
+        <v/>
+      </c>
+      <c r="E4" t="str">
+        <v/>
       </c>
       <c r="F4">
-        <v>3.4</v>
-      </c>
-      <c r="G4" t="str">
-        <v/>
+        <v>11.2</v>
       </c>
     </row>
     <row r="5">
@@ -519,123 +506,105 @@
       <c r="F5" t="str">
         <v/>
       </c>
-      <c r="G5">
-        <v>11.2</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v/>
+        <v>购物时间</v>
       </c>
       <c r="B6" t="str">
-        <v/>
+        <v>超市名称</v>
       </c>
       <c r="C6" t="str">
-        <v/>
+        <v>商品名称</v>
       </c>
       <c r="D6" t="str">
-        <v/>
+        <v>数量</v>
       </c>
       <c r="E6" t="str">
-        <v/>
+        <v>单价</v>
       </c>
       <c r="F6" t="str">
-        <v/>
-      </c>
-      <c r="G6" t="str">
-        <v/>
+        <v>小计</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
+        <v>2026-03-23 10:04:51</v>
+      </c>
+      <c r="B7" t="str">
         <v>大利家精品超市谢村店</v>
       </c>
-      <c r="B7" t="str">
-        <v>2026-03-23 10:04:51</v>
-      </c>
       <c r="C7" t="str">
-        <v/>
-      </c>
-      <c r="D7" t="str">
-        <v/>
-      </c>
-      <c r="E7" t="str">
-        <v/>
-      </c>
-      <c r="F7" t="str">
-        <v/>
-      </c>
-      <c r="G7" t="str">
-        <v/>
+        <v>鸡腿</v>
+      </c>
+      <c r="D7">
+        <v>1</v>
+      </c>
+      <c r="E7">
+        <v>7.8</v>
+      </c>
+      <c r="F7">
+        <v>7.8</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v/>
+        <v>2026-03-23 10:04:51</v>
       </c>
       <c r="B8" t="str">
-        <v/>
+        <v>大利家精品超市谢村店</v>
       </c>
       <c r="C8" t="str">
-        <v>商品名称</v>
-      </c>
-      <c r="D8" t="str">
-        <v>单价</v>
-      </c>
-      <c r="E8" t="str">
-        <v>数量</v>
-      </c>
-      <c r="F8" t="str">
-        <v>小计</v>
-      </c>
-      <c r="G8" t="str">
-        <v/>
+        <v>蔬菜鹿茸菇</v>
+      </c>
+      <c r="D8">
+        <v>1</v>
+      </c>
+      <c r="E8">
+        <v>5.5</v>
+      </c>
+      <c r="F8">
+        <v>5.5</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v/>
+        <v>2026-03-23 10:04:51</v>
       </c>
       <c r="B9" t="str">
-        <v/>
+        <v>大利家精品超市谢村店</v>
       </c>
       <c r="C9" t="str">
-        <v>鸡腿</v>
+        <v>珍珠苦瓜</v>
       </c>
       <c r="D9">
-        <v>7.8</v>
+        <v>1</v>
       </c>
       <c r="E9">
-        <v>1</v>
+        <v>3.1</v>
       </c>
       <c r="F9">
-        <v>7.8</v>
-      </c>
-      <c r="G9" t="str">
-        <v/>
+        <v>3.1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v/>
+        <v>2026-03-23 10:04:51</v>
       </c>
       <c r="B10" t="str">
-        <v/>
+        <v>大利家精品超市谢村店</v>
       </c>
       <c r="C10" t="str">
-        <v>蔬菜鹿茸菇</v>
-      </c>
-      <c r="D10">
-        <v>5.5</v>
-      </c>
-      <c r="E10">
-        <v>1</v>
+        <v>合计</v>
+      </c>
+      <c r="D10" t="str">
+        <v/>
+      </c>
+      <c r="E10" t="str">
+        <v/>
       </c>
       <c r="F10">
-        <v>5.5</v>
-      </c>
-      <c r="G10" t="str">
-        <v/>
+        <v>16.4</v>
       </c>
     </row>
     <row r="11">
@@ -646,70 +615,21 @@
         <v/>
       </c>
       <c r="C11" t="str">
-        <v>珍珠苦瓜</v>
-      </c>
-      <c r="D11">
-        <v>3.1</v>
-      </c>
-      <c r="E11">
-        <v>1</v>
-      </c>
-      <c r="F11">
-        <v>3.1</v>
-      </c>
-      <c r="G11" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v/>
-      </c>
-      <c r="B12" t="str">
-        <v/>
-      </c>
-      <c r="C12" t="str">
-        <v/>
-      </c>
-      <c r="D12" t="str">
-        <v/>
-      </c>
-      <c r="E12" t="str">
-        <v/>
-      </c>
-      <c r="F12" t="str">
-        <v/>
-      </c>
-      <c r="G12">
-        <v>16.4</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v/>
-      </c>
-      <c r="B13" t="str">
-        <v/>
-      </c>
-      <c r="C13" t="str">
-        <v/>
-      </c>
-      <c r="D13" t="str">
-        <v/>
-      </c>
-      <c r="E13" t="str">
-        <v/>
-      </c>
-      <c r="F13" t="str">
-        <v/>
-      </c>
-      <c r="G13" t="str">
+        <v/>
+      </c>
+      <c r="D11" t="str">
+        <v/>
+      </c>
+      <c r="E11" t="str">
+        <v/>
+      </c>
+      <c r="F11" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G13"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F11"/>
   </ignoredErrors>
 </worksheet>
 </file>